--- a/moduli_aziende/aifecs/moduli_compilati/MOD-710-E-Conoscenza_Organizzativa.xlsx
+++ b/moduli_aziende/aifecs/moduli_compilati/MOD-710-E-Conoscenza_Organizzativa.xlsx
@@ -2,26 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R51fa1bd70e3742f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc89970507b2f4293"/>
   </x:sheets>
 </x:workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author/>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>AIFECS — BOZZA DA CONFERMARE. Proposta operativa per il sistema qualità ISO 9001. Ruoli, priorità, criteri e obiettivi sono proposte. I registri vanno compilati con dati ed evidenze reali. Vedere la guida e la proposta operativa del pacchetto.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -437,9 +420,7 @@
       <x:c r="F2" s="7" t="str">
         <x:v>DID</x:v>
       </x:c>
-      <x:c r="G2" s="7" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="G2" s="7"/>
     </x:row>
     <x:row r="3" ht="50" customHeight="1">
       <x:c r="A3" s="6"/>
@@ -458,9 +439,7 @@
       <x:c r="F3" s="7" t="str">
         <x:v>DID</x:v>
       </x:c>
-      <x:c r="G3" s="7" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="G3" s="7"/>
     </x:row>
     <x:row r="4" ht="50" customHeight="1">
       <x:c r="A4" s="6"/>
@@ -479,9 +458,7 @@
       <x:c r="F4" s="7" t="str">
         <x:v>DID</x:v>
       </x:c>
-      <x:c r="G4" s="7" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="G4" s="7"/>
     </x:row>
     <x:row r="5" ht="50" customHeight="1">
       <x:c r="A5" s="6"/>
@@ -500,9 +477,7 @@
       <x:c r="F5" s="7" t="str">
         <x:v>SOC</x:v>
       </x:c>
-      <x:c r="G5" s="7" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="G5" s="7"/>
     </x:row>
     <x:row r="6" ht="50" customHeight="1">
       <x:c r="A6" s="6"/>
@@ -521,9 +496,7 @@
       <x:c r="F6" s="7" t="str">
         <x:v>SEG</x:v>
       </x:c>
-      <x:c r="G6" s="7" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="G6" s="7"/>
     </x:row>
     <x:row r="7" ht="50" customHeight="1">
       <x:c r="A7" s="6"/>
@@ -542,9 +515,7 @@
       <x:c r="F7" s="7" t="str">
         <x:v>SEG / TUT</x:v>
       </x:c>
-      <x:c r="G7" s="7" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="G7" s="7"/>
     </x:row>
     <x:row r="8" ht="50" customHeight="1">
       <x:c r="A8" s="6"/>
@@ -563,9 +534,7 @@
       <x:c r="F8" s="7" t="str">
         <x:v>DID / SEG</x:v>
       </x:c>
-      <x:c r="G8" s="7" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="G8" s="7"/>
     </x:row>
     <x:row r="9" ht="50" customHeight="1">
       <x:c r="A9" s="6"/>
@@ -584,9 +553,7 @@
       <x:c r="F9" s="7" t="str">
         <x:v>IT</x:v>
       </x:c>
-      <x:c r="G9" s="7" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="G9" s="7"/>
     </x:row>
     <x:row r="10" ht="50" customHeight="1">
       <x:c r="A10" s="6"/>
@@ -605,9 +572,7 @@
       <x:c r="F10" s="7" t="str">
         <x:v>QUAL</x:v>
       </x:c>
-      <x:c r="G10" s="7" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="G10" s="7"/>
     </x:row>
     <x:row r="11" ht="50" customHeight="1">
       <x:c r="A11" s="6"/>
@@ -626,9 +591,7 @@
       <x:c r="F11" s="7" t="str">
         <x:v>DIR / IT</x:v>
       </x:c>
-      <x:c r="G11" s="7" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="G11" s="7"/>
     </x:row>
     <x:row r="12" ht="50" customHeight="1">
       <x:c r="A12" s="6"/>
@@ -647,9 +610,7 @@
       <x:c r="F12" s="7" t="str">
         <x:v>SOC</x:v>
       </x:c>
-      <x:c r="G12" s="7" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="G12" s="7"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="2"/>
@@ -860,6 +821,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b441ee554ba4881"/>
 </x:worksheet>
 </file>